--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.56471846377107</v>
+        <v>4.479266750362799</v>
       </c>
       <c r="D2" t="n">
-        <v>12.49498409935183</v>
+        <v>2.030434916144672</v>
       </c>
       <c r="E2" t="n">
-        <v>9.088251715455581</v>
+        <v>1.476840903761532</v>
       </c>
       <c r="F2" t="n">
-        <v>10.76126143709921</v>
+        <v>1.748704983528623</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.08089817771718</v>
+        <v>5.050645953879043</v>
       </c>
       <c r="D3" t="n">
-        <v>39.61322256621791</v>
+        <v>6.43714866701041</v>
       </c>
       <c r="E3" t="n">
-        <v>9.088251715455581</v>
+        <v>1.476840903761532</v>
       </c>
       <c r="F3" t="n">
-        <v>10.76126143709921</v>
+        <v>1.748704983528623</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.9269722280108</v>
+        <v>3.888132987051755</v>
       </c>
       <c r="D4" t="n">
-        <v>14.30471950091997</v>
+        <v>2.324516918899495</v>
       </c>
       <c r="E4" t="n">
-        <v>9.088251715455581</v>
+        <v>1.476840903761532</v>
       </c>
       <c r="F4" t="n">
-        <v>10.76126143709921</v>
+        <v>1.748704983528623</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.365046649794032</v>
+        <v>1.19682008059153</v>
       </c>
       <c r="D5" t="n">
-        <v>19.98124120268809</v>
+        <v>3.246951695436814</v>
       </c>
       <c r="E5" t="n">
-        <v>9.088251715455581</v>
+        <v>1.476840903761532</v>
       </c>
       <c r="F5" t="n">
-        <v>10.76126143709921</v>
+        <v>1.748704983528623</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
